--- a/Stock Analysis/RodWal Terminal/Business Case.xlsx
+++ b/Stock Analysis/RodWal Terminal/Business Case.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rodwals-my.sharepoint.com/personal/samuel_rodwal_com/Documents/Professional_WorkTools/Github/RodWal-Capital-Insights/Stock Analysis/RodWal Terminal/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{CED6647D-C784-4C35-801B-5114A18723A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2613B3C8-C24F-4ED5-9C6C-E8D95F10270D}"/>
+  <xr:revisionPtr revIDLastSave="48" documentId="8_{CED6647D-C784-4C35-801B-5114A18723A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5BE6A4CF-846D-44C6-9633-FCE3F2DEED03}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Initial Parameters" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="190">
   <si>
     <t>## Initial Parameters</t>
   </si>
@@ -358,84 +358,24 @@
     <t>## APP Blueprint</t>
   </si>
   <si>
-    <t>Structure</t>
-  </si>
-  <si>
-    <t>Level Description</t>
-  </si>
-  <si>
-    <t>Module/Submodule/File</t>
-  </si>
-  <si>
-    <t>Functionality</t>
-  </si>
-  <si>
     <t>rodwal_terminal/</t>
   </si>
   <si>
-    <t>Project root</t>
-  </si>
-  <si>
     <t>core/</t>
   </si>
   <si>
-    <t>Cross-cutting</t>
-  </si>
-  <si>
-    <t>theme.py, config.py, logging.py, scheduler.py</t>
-  </si>
-  <si>
-    <t>Colors, settings, log setup, periodic jobs</t>
-  </si>
-  <si>
     <t>data_providers/</t>
   </si>
   <si>
-    <t>Market data layer</t>
-  </si>
-  <si>
-    <t>base.py, yahoo.py, polygon.py (opt)</t>
-  </si>
-  <si>
-    <t>Unified API: get_quotes, get_fundamentals, get_news</t>
-  </si>
-  <si>
     <t>modules/</t>
   </si>
   <si>
-    <t>Domain modules</t>
-  </si>
-  <si>
-    <t>markets.py, portfolio.py, screener.py, news.py, econ.py</t>
-  </si>
-  <si>
-    <t>Business logic per feature</t>
-  </si>
-  <si>
     <t>ui/</t>
   </si>
   <si>
-    <t>Presentation</t>
-  </si>
-  <si>
-    <t>terminal.py, views/*</t>
-  </si>
-  <si>
-    <t>Tk shell, command router, views, widgets</t>
-  </si>
-  <si>
     <t>config/</t>
   </si>
   <si>
-    <t>Artifacts</t>
-  </si>
-  <si>
-    <t>markets.json, settings.json</t>
-  </si>
-  <si>
-    <t>Watchlist &amp; user settings</t>
-  </si>
-  <si>
     <t>tests/</t>
   </si>
   <si>
@@ -445,9 +385,6 @@
     <t>test_*.py</t>
   </si>
   <si>
-    <t>Unit/integration tests</t>
-  </si>
-  <si>
     <t>## Deliverables</t>
   </si>
   <si>
@@ -521,6 +458,179 @@
   </si>
   <si>
     <t>Saved filters, factor definitions, and example outputs</t>
+  </si>
+  <si>
+    <t>(Project Root)</t>
+  </si>
+  <si>
+    <t>Main application directory</t>
+  </si>
+  <si>
+    <t>__init__.py</t>
+  </si>
+  <si>
+    <t>Initialization file for core module</t>
+  </si>
+  <si>
+    <t>theme.py</t>
+  </si>
+  <si>
+    <t>Stores Terminal's colour palette</t>
+  </si>
+  <si>
+    <t>config.py</t>
+  </si>
+  <si>
+    <t>Application settings and configuration</t>
+  </si>
+  <si>
+    <t>logging.py</t>
+  </si>
+  <si>
+    <t>Logging setup and configuration</t>
+  </si>
+  <si>
+    <t>scheduler.py</t>
+  </si>
+  <si>
+    <t>Periodic job scheduler</t>
+  </si>
+  <si>
+    <t>Initialization file for data providers</t>
+  </si>
+  <si>
+    <t>base.py</t>
+  </si>
+  <si>
+    <t>Base class for market data APIs</t>
+  </si>
+  <si>
+    <t>yahoo.py</t>
+  </si>
+  <si>
+    <t>Yahoo Finance integration</t>
+  </si>
+  <si>
+    <r>
+      <t>polygon.py</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(optional)</t>
+    </r>
+  </si>
+  <si>
+    <t>Polygon.io integration</t>
+  </si>
+  <si>
+    <t>Initialization file for domain modules</t>
+  </si>
+  <si>
+    <t>markets.py</t>
+  </si>
+  <si>
+    <t>Market overview and data logic</t>
+  </si>
+  <si>
+    <t>portfolio.py</t>
+  </si>
+  <si>
+    <t>Portfolio management logic</t>
+  </si>
+  <si>
+    <t>screener.py</t>
+  </si>
+  <si>
+    <t>Stock screener functionality</t>
+  </si>
+  <si>
+    <t>news.py</t>
+  </si>
+  <si>
+    <t>News aggregation and processing</t>
+  </si>
+  <si>
+    <t>econ.py</t>
+  </si>
+  <si>
+    <t>Economic indicators and data</t>
+  </si>
+  <si>
+    <t>terminal.py</t>
+  </si>
+  <si>
+    <t>Tkinter shell and command router</t>
+  </si>
+  <si>
+    <t>views/</t>
+  </si>
+  <si>
+    <t>UI views and widgets</t>
+  </si>
+  <si>
+    <t>views/*.py</t>
+  </si>
+  <si>
+    <t>Individual view components</t>
+  </si>
+  <si>
+    <t>markets.json</t>
+  </si>
+  <si>
+    <t>Market watchlist configuration</t>
+  </si>
+  <si>
+    <t>settings.json</t>
+  </si>
+  <si>
+    <t>User preferences and settings</t>
+  </si>
+  <si>
+    <t>Unit and integration tests</t>
+  </si>
+  <si>
+    <t>Folder Structure</t>
+  </si>
+  <si>
+    <t>charts.py</t>
+  </si>
+  <si>
+    <t>Displays financial information in charts</t>
+  </si>
+  <si>
+    <t>helper_extensions.py</t>
+  </si>
+  <si>
+    <t>Stores helper functions (e.i Format $T, $B, $M..)</t>
+  </si>
+  <si>
+    <t>FinancialModelingPrep.py</t>
+  </si>
+  <si>
+    <t>FMP API Integration</t>
+  </si>
+  <si>
+    <t>portfolio.json</t>
+  </si>
+  <si>
+    <t>Portfolio configurations (Depoits Phasing &amp; Resource allocation)</t>
   </si>
 </sst>
 </file>
@@ -530,7 +640,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -544,6 +654,22 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -553,7 +679,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -561,11 +687,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -575,6 +716,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -590,6 +735,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1445,13 +1594,17 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="51.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="60" customWidth="1"/>
+    <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
+    <col min="6" max="6" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.5703125" customWidth="1"/>
+    <col min="8" max="8" width="35.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1460,112 +1613,248 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>109</v>
+      <c r="A2" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="5" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C4" t="s">
+        <v>142</v>
+      </c>
+      <c r="D4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D6" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>148</v>
+      </c>
+      <c r="D7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D8" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>184</v>
+      </c>
+      <c r="D9" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" t="s">
+        <v>142</v>
+      </c>
+      <c r="D10" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>153</v>
+      </c>
+      <c r="D11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
+        <v>155</v>
+      </c>
+      <c r="D12" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C13" t="s">
+        <v>186</v>
+      </c>
+      <c r="D13" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C14" t="s">
+        <v>157</v>
+      </c>
+      <c r="D14" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>109</v>
+      </c>
+      <c r="C15" t="s">
+        <v>142</v>
+      </c>
+      <c r="D15" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C16" t="s">
+        <v>160</v>
+      </c>
+      <c r="D16" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C17" t="s">
+        <v>182</v>
+      </c>
+      <c r="D17" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C18" t="s">
+        <v>162</v>
+      </c>
+      <c r="D18" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C19" t="s">
+        <v>164</v>
+      </c>
+      <c r="D19" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C20" t="s">
+        <v>166</v>
+      </c>
+      <c r="D20" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C21" t="s">
+        <v>168</v>
+      </c>
+      <c r="D21" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
         <v>110</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C22" t="s">
+        <v>170</v>
+      </c>
+      <c r="D22" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C23" t="s">
+        <v>172</v>
+      </c>
+      <c r="D23" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C24" t="s">
+        <v>174</v>
+      </c>
+      <c r="D24" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="C25" t="s">
+        <v>176</v>
+      </c>
+      <c r="D25" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C26" t="s">
+        <v>188</v>
+      </c>
+      <c r="D26" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C27" t="s">
+        <v>178</v>
+      </c>
+      <c r="D27" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
         <v>112</v>
       </c>
-      <c r="B4" t="s">
-        <v>113</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="C28" t="s">
         <v>114</v>
       </c>
-      <c r="D4" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>116</v>
-      </c>
-      <c r="B5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C5" t="s">
-        <v>118</v>
-      </c>
-      <c r="D5" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>120</v>
-      </c>
-      <c r="B6" t="s">
-        <v>121</v>
-      </c>
-      <c r="C6" t="s">
-        <v>122</v>
-      </c>
-      <c r="D6" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>124</v>
-      </c>
-      <c r="B7" t="s">
-        <v>125</v>
-      </c>
-      <c r="C7" t="s">
-        <v>126</v>
-      </c>
-      <c r="D7" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>128</v>
-      </c>
-      <c r="B8" t="s">
-        <v>129</v>
-      </c>
-      <c r="C8" t="s">
-        <v>130</v>
-      </c>
-      <c r="D8" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>132</v>
-      </c>
-      <c r="B9" t="s">
-        <v>133</v>
-      </c>
-      <c r="C9" t="s">
-        <v>134</v>
-      </c>
-      <c r="D9" t="s">
-        <v>135</v>
+      <c r="D28" t="s">
+        <v>180</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1582,51 +1871,51 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>137</v>
+        <v>116</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>140</v>
+        <v>119</v>
       </c>
       <c r="B3" t="s">
-        <v>141</v>
+        <v>120</v>
       </c>
       <c r="C3" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>143</v>
+        <v>122</v>
       </c>
       <c r="B4" t="s">
-        <v>144</v>
+        <v>123</v>
       </c>
       <c r="C4" t="s">
-        <v>145</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="B5" t="s">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="C5" t="s">
-        <v>148</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1634,10 +1923,10 @@
         <v>101</v>
       </c>
       <c r="B6" t="s">
-        <v>149</v>
+        <v>128</v>
       </c>
       <c r="C6" t="s">
-        <v>150</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1645,43 +1934,43 @@
         <v>101</v>
       </c>
       <c r="B7" t="s">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="C7" t="s">
-        <v>152</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>113</v>
+      </c>
+      <c r="B8" t="s">
+        <v>132</v>
+      </c>
+      <c r="C8" t="s">
         <v>133</v>
-      </c>
-      <c r="B8" t="s">
-        <v>153</v>
-      </c>
-      <c r="C8" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="B9" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="C9" t="s">
-        <v>157</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>158</v>
+        <v>137</v>
       </c>
       <c r="B10" t="s">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="C10" t="s">
-        <v>160</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>

--- a/Stock Analysis/RodWal Terminal/Business Case.xlsx
+++ b/Stock Analysis/RodWal Terminal/Business Case.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rodwals-my.sharepoint.com/personal/samuel_rodwal_com/Documents/Professional_WorkTools/Github/RodWal-Capital-Insights/Stock Analysis/RodWal Terminal/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="8_{CED6647D-C784-4C35-801B-5114A18723A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5BE6A4CF-846D-44C6-9633-FCE3F2DEED03}"/>
+  <xr:revisionPtr revIDLastSave="49" documentId="8_{CED6647D-C784-4C35-801B-5114A18723A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C907E87-E423-4B25-B8D5-7337AC70A718}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="16410" windowHeight="10515" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Initial Parameters" sheetId="1" r:id="rId1"/>
@@ -735,10 +735,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1599,7 +1595,7 @@
   <cols>
     <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="35.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.7109375" customWidth="1"/>
     <col min="6" max="6" width="20.5703125" bestFit="1" customWidth="1"/>
